--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7366377496576</v>
+        <v>9.70720363431936</v>
       </c>
       <c r="D2" t="n">
-        <v>58.32306672984733</v>
+        <v>9.477498343600191</v>
       </c>
       <c r="E2" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F2" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>75.70696215075176</v>
+        <v>12.30238134949716</v>
       </c>
       <c r="D3" t="n">
-        <v>74.11836072937443</v>
+        <v>12.04423361852334</v>
       </c>
       <c r="E3" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F3" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.94282299911545</v>
+        <v>10.22820873735626</v>
       </c>
       <c r="D4" t="n">
-        <v>61.36843806191472</v>
+        <v>9.972371185061142</v>
       </c>
       <c r="E4" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F4" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.46469202075087</v>
+        <v>8.688012453372018</v>
       </c>
       <c r="D5" t="n">
-        <v>51.88356697072538</v>
+        <v>8.431079632742874</v>
       </c>
       <c r="E5" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F5" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.09077356990205</v>
+        <v>10.08975070510908</v>
       </c>
       <c r="D6" t="n">
-        <v>62.50649266800244</v>
+        <v>10.1573050585504</v>
       </c>
       <c r="E6" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F6" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.86782484804731</v>
+        <v>6.153521537807688</v>
       </c>
       <c r="D7" t="n">
-        <v>37.91498061201708</v>
+        <v>6.161184349452776</v>
       </c>
       <c r="E7" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F7" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.67945174404833</v>
+        <v>4.822910908407853</v>
       </c>
       <c r="D8" t="n">
-        <v>29.51506744218786</v>
+        <v>4.796198459355526</v>
       </c>
       <c r="E8" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F8" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.83077493153818</v>
+        <v>6.147500926374954</v>
       </c>
       <c r="D9" t="n">
-        <v>36.2817316483894</v>
+        <v>5.895781392863277</v>
       </c>
       <c r="E9" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F9" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.45986607754031</v>
+        <v>10.7997282376003</v>
       </c>
       <c r="D10" t="n">
-        <v>67.69049699874326</v>
+        <v>10.99970576229578</v>
       </c>
       <c r="E10" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F10" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.79335502010858</v>
+        <v>3.703920190767644</v>
       </c>
       <c r="D11" t="n">
-        <v>23.67085610438183</v>
+        <v>3.846514116962047</v>
       </c>
       <c r="E11" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F11" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.46722304031587</v>
+        <v>9.500923744051329</v>
       </c>
       <c r="D12" t="n">
-        <v>58.9519936939738</v>
+        <v>9.579698975270743</v>
       </c>
       <c r="E12" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F12" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.7408060245709</v>
+        <v>8.732880978992771</v>
       </c>
       <c r="D13" t="n">
-        <v>54.81882479026807</v>
+        <v>8.908059028418561</v>
       </c>
       <c r="E13" t="n">
-        <v>15.41208951318875</v>
+        <v>2.504464545893172</v>
       </c>
       <c r="F13" t="n">
-        <v>15.21887624222896</v>
+        <v>2.473067389362206</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
